--- a/Data/FRB_Kritti.xlsx
+++ b/Data/FRB_Kritti.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\Research\FRB\cosmology\FRB_cosmology\code\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0E07D778-A783-4DB6-91E8-55FED20063F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B62EC12-939E-49FC-BDCD-929C7B58955E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{99AB83C2-A40F-4968-A7DC-7E5884487DA1}"/>
   </bookViews>
   <sheets>
     <sheet name="FRB_Kritti" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -310,98 +310,99 @@
     <t>274.2278, 69.7222</t>
   </si>
   <si>
+    <t>FRB 20230712A</t>
+  </si>
+  <si>
+    <t>11h51m07.52s +71d41m44.3s</t>
+  </si>
+  <si>
+    <t>167.360311, 72.558011</t>
+  </si>
+  <si>
+    <t>11 09 26.4746, +72 33 28.8396</t>
+  </si>
+  <si>
+    <t>FRB 20220310F</t>
+  </si>
+  <si>
+    <t>22h40m06.52s +70d55m19.82s</t>
+  </si>
+  <si>
+    <t>134.721078150, 73.491016090</t>
+  </si>
+  <si>
+    <t>8:58:53.0539, +73:29:27.445</t>
+  </si>
+  <si>
+    <t>FRB 20230216A</t>
+  </si>
+  <si>
+    <t>15h42m31.10s +71d08m00.77s</t>
+  </si>
+  <si>
+    <t>156.473172090, 3.436834140</t>
+  </si>
+  <si>
+    <t>10:25:53.5613, +3:26:12.603</t>
+  </si>
+  <si>
+    <t>FRB 20221027A</t>
+  </si>
+  <si>
+    <t>11h07m08.81s +72d16m54.64s</t>
+  </si>
+  <si>
+    <t>130.873, 72.1009</t>
+  </si>
+  <si>
+    <t>08:43:29.52, 72:06:03.24</t>
+  </si>
+  <si>
+    <t>FRB 20221219A</t>
+  </si>
+  <si>
+    <t>11h09m26.047s   +72d33m28.02s</t>
+  </si>
+  <si>
+    <t>257.6296, 71.6266</t>
+  </si>
+  <si>
+    <t>17:10:31.10, 71:37:35.76</t>
+  </si>
+  <si>
+    <t>FRB 20220418A</t>
+  </si>
+  <si>
+    <t>09h35m56.15s +73d17m04.8s</t>
+  </si>
+  <si>
+    <t>219.106487310, 70.095317150</t>
+  </si>
+  <si>
+    <t>14:36:25.5844, +70:05:43.597</t>
+  </si>
+  <si>
+    <t>FRB 20221029A</t>
+  </si>
+  <si>
+    <t>16h10m09.16s +70d47m06.2s</t>
+  </si>
+  <si>
+    <t>141.966300, 72.452000</t>
+  </si>
+  <si>
+    <t>09:27:51.9120, +72:27:07.199</t>
+  </si>
+  <si>
     <t>18:16:54.67, +69:43:19.92</t>
-  </si>
-  <si>
-    <t>FRB 20230712A</t>
-  </si>
-  <si>
-    <t>11h51m07.52s +71d41m44.3s</t>
-  </si>
-  <si>
-    <t>167.360311, 72.558011</t>
-  </si>
-  <si>
-    <t>11 09 26.4746, +72 33 28.8396</t>
-  </si>
-  <si>
-    <t>FRB 20220310F</t>
-  </si>
-  <si>
-    <t>22h40m06.52s +70d55m19.82s</t>
-  </si>
-  <si>
-    <t>134.721078150, 73.491016090</t>
-  </si>
-  <si>
-    <t>8:58:53.0539, +73:29:27.445</t>
-  </si>
-  <si>
-    <t>FRB 20230216A</t>
-  </si>
-  <si>
-    <t>15h42m31.10s +71d08m00.77s</t>
-  </si>
-  <si>
-    <t>156.473172090, 3.436834140</t>
-  </si>
-  <si>
-    <t>10:25:53.5613, +3:26:12.603</t>
-  </si>
-  <si>
-    <t>FRB 20221027A</t>
-  </si>
-  <si>
-    <t>11h07m08.81s +72d16m54.64s</t>
-  </si>
-  <si>
-    <t>130.873, 72.1009</t>
-  </si>
-  <si>
-    <t>08:43:29.52, 72:06:03.24</t>
-  </si>
-  <si>
-    <t>FRB 20221219A</t>
-  </si>
-  <si>
-    <t>11h09m26.047s   +72d33m28.02s</t>
-  </si>
-  <si>
-    <t>257.6296, 71.6266</t>
-  </si>
-  <si>
-    <t>17:10:31.10, 71:37:35.76</t>
-  </si>
-  <si>
-    <t>FRB 20220418A</t>
-  </si>
-  <si>
-    <t>09h35m56.15s +73d17m04.8s</t>
-  </si>
-  <si>
-    <t>219.106487310, 70.095317150</t>
-  </si>
-  <si>
-    <t>14:36:25.5844, +70:05:43.597</t>
-  </si>
-  <si>
-    <t>FRB 20221029A</t>
-  </si>
-  <si>
-    <t>16h10m09.16s +70d47m06.2s</t>
-  </si>
-  <si>
-    <t>141.966300, 72.452000</t>
-  </si>
-  <si>
-    <t>09:27:51.9120, +72:27:07.199</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -561,6 +562,18 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -865,7 +878,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -992,16 +1005,19 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1023,6 +1039,7 @@
     <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="42" xr:uid="{5591EC47-721F-4E07-ADC5-8023F4A424BC}"/>
     <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
     <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
@@ -1388,17 +1405,17 @@
       <c r="B2">
         <v>0.4012</v>
       </c>
-      <c r="C2">
-        <v>788.8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>94</v>
+      <c r="C2" s="2">
+        <v>559.42999999999995</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="E2" t="s">
         <v>95</v>
       </c>
       <c r="F2" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -1408,11 +1425,11 @@
       <c r="B3">
         <v>4.3299999999999998E-2</v>
       </c>
-      <c r="C3">
-        <v>346.65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
+      <c r="C3" s="2">
+        <v>182.98</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
@@ -1428,11 +1445,11 @@
       <c r="B4">
         <v>0.35099999999999998</v>
       </c>
-      <c r="C4">
-        <v>496.8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>82</v>
+      <c r="C4" s="2">
+        <v>346.65</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="E4" t="s">
         <v>83</v>
@@ -1442,17 +1459,17 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B5">
         <v>0.24809999999999999</v>
       </c>
-      <c r="C5">
-        <v>601.37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>46</v>
+      <c r="C5" s="2">
+        <v>363.43</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E5" t="s">
         <v>47</v>
@@ -1463,22 +1480,22 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6">
         <v>0.47799999999999998</v>
       </c>
-      <c r="C6">
-        <v>413</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="2">
+        <v>416.71</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
         <v>102</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>103</v>
-      </c>
-      <c r="F6" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -1488,11 +1505,11 @@
       <c r="B7">
         <v>1.12E-2</v>
       </c>
-      <c r="C7">
-        <v>559.42999999999995</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
+      <c r="C7" s="2">
+        <v>-22.31</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1508,11 +1525,11 @@
       <c r="B8">
         <v>0.37140000000000001</v>
       </c>
-      <c r="C8">
-        <v>551.1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>90</v>
+      <c r="C8" s="2">
+        <v>428.75</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="E8" t="s">
         <v>91</v>
@@ -1523,22 +1540,22 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B9">
         <v>0.62129999999999996</v>
       </c>
-      <c r="C9">
-        <v>395.8</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="2">
+        <v>585.84</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
         <v>118</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>119</v>
-      </c>
-      <c r="F9" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -1548,11 +1565,11 @@
       <c r="B10">
         <v>0.3004</v>
       </c>
-      <c r="C10">
-        <v>1347.42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>70</v>
+      <c r="C10" s="2">
+        <v>307.81</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="E10" t="s">
         <v>71</v>
@@ -1568,11 +1585,11 @@
       <c r="B11">
         <v>8.9399999999999993E-2</v>
       </c>
-      <c r="C11">
-        <v>363.43</v>
-      </c>
-      <c r="D11" t="s">
-        <v>19</v>
+      <c r="C11" s="2">
+        <v>214.29</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -1588,11 +1605,11 @@
       <c r="B12">
         <v>0.3619</v>
       </c>
-      <c r="C12">
-        <v>662.3</v>
-      </c>
-      <c r="D12" t="s">
-        <v>86</v>
+      <c r="C12" s="2">
+        <v>601.37</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="E12" t="s">
         <v>87</v>
@@ -1608,11 +1625,11 @@
       <c r="B13">
         <v>0.2414</v>
       </c>
-      <c r="C13">
-        <v>214.29</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
+      <c r="C13" s="2">
+        <v>571.5</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="E13" t="s">
         <v>43</v>
@@ -1628,11 +1645,11 @@
       <c r="B14">
         <v>0.1139</v>
       </c>
-      <c r="C14">
-        <v>-22.31</v>
-      </c>
-      <c r="D14" t="s">
-        <v>27</v>
+      <c r="C14" s="2">
+        <v>575.86</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
@@ -1648,11 +1665,11 @@
       <c r="B15">
         <v>0.15820000000000001</v>
       </c>
-      <c r="C15">
-        <v>585.84</v>
-      </c>
-      <c r="D15" t="s">
-        <v>34</v>
+      <c r="C15" s="2">
+        <v>274.68</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="E15" t="s">
         <v>35</v>
@@ -1668,11 +1685,11 @@
       <c r="B16">
         <v>0.28470000000000001</v>
       </c>
-      <c r="C16">
-        <v>405.36</v>
-      </c>
-      <c r="D16" t="s">
-        <v>66</v>
+      <c r="C16" s="2">
+        <v>387.85</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E16" t="s">
         <v>67</v>
@@ -1683,42 +1700,42 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B17">
         <v>0.54220000000000002</v>
       </c>
-      <c r="C17">
-        <v>306.35000000000002</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C17" s="2">
+        <v>405.36</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" t="s">
         <v>110</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>111</v>
-      </c>
-      <c r="F17" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B18">
         <v>0.97499999999999998</v>
       </c>
-      <c r="C18">
-        <v>356.1</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="C18" s="2">
+        <v>1347.42</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
         <v>122</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>123</v>
-      </c>
-      <c r="F18" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -1728,11 +1745,11 @@
       <c r="B19">
         <v>0.23949999999999999</v>
       </c>
-      <c r="C19">
-        <v>307.81</v>
-      </c>
-      <c r="D19" t="s">
-        <v>38</v>
+      <c r="C19" s="2">
+        <v>366.21100000000001</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="E19" t="s">
         <v>39</v>
@@ -1748,11 +1765,11 @@
       <c r="B20">
         <v>0.2505</v>
       </c>
-      <c r="C20">
-        <v>571.5</v>
-      </c>
-      <c r="D20" t="s">
-        <v>50</v>
+      <c r="C20" s="2">
+        <v>323.5</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="E20" t="s">
         <v>51</v>
@@ -1768,11 +1785,11 @@
       <c r="B21">
         <v>0.27639999999999998</v>
       </c>
-      <c r="C21">
-        <v>387.85</v>
-      </c>
-      <c r="D21" t="s">
-        <v>62</v>
+      <c r="C21" s="2">
+        <v>496.8</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="E21" t="s">
         <v>63</v>
@@ -1783,22 +1800,22 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B22">
         <v>0.55300000000000005</v>
       </c>
-      <c r="C22">
-        <v>548.21</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C22" s="2">
+        <v>662.3</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" t="s">
         <v>114</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>115</v>
-      </c>
-      <c r="F22" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1808,11 +1825,11 @@
       <c r="B23">
         <v>9.3899999999999997E-2</v>
       </c>
-      <c r="C23">
-        <v>416.71</v>
-      </c>
-      <c r="D23" t="s">
-        <v>23</v>
+      <c r="C23" s="2">
+        <v>551.1</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="E23" t="s">
         <v>24</v>
@@ -1823,22 +1840,22 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B24">
         <v>0.53100000000000003</v>
       </c>
-      <c r="C24">
-        <v>411.9</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C24" s="2">
+        <v>788.8</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" t="s">
         <v>106</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>107</v>
-      </c>
-      <c r="F24" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -1848,11 +1865,11 @@
       <c r="B25">
         <v>0.27060000000000001</v>
       </c>
-      <c r="C25">
-        <v>274.68</v>
-      </c>
-      <c r="D25" t="s">
-        <v>58</v>
+      <c r="C25" s="2">
+        <v>580.65</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="E25" t="s">
         <v>59</v>
@@ -1868,11 +1885,11 @@
       <c r="B26">
         <v>0.30149999999999999</v>
       </c>
-      <c r="C26">
-        <v>366.21100000000001</v>
-      </c>
-      <c r="D26" t="s">
-        <v>74</v>
+      <c r="C26" s="2">
+        <v>413</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="E26" t="s">
         <v>75</v>
@@ -1888,11 +1905,11 @@
       <c r="B27">
         <v>0.32700000000000001</v>
       </c>
-      <c r="C27">
-        <v>323.5</v>
-      </c>
-      <c r="D27" t="s">
-        <v>78</v>
+      <c r="C27" s="2">
+        <v>411.9</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="E27" t="s">
         <v>79</v>
@@ -1908,11 +1925,11 @@
       <c r="B28">
         <v>0.127</v>
       </c>
-      <c r="C28">
-        <v>428.75</v>
-      </c>
-      <c r="D28" t="s">
-        <v>31</v>
+      <c r="C28" s="2">
+        <v>306.35000000000002</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="E28" t="s">
         <v>28</v>
@@ -1923,22 +1940,22 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B29">
         <v>0.45250000000000001</v>
       </c>
-      <c r="C29">
-        <v>580.65</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="C29" s="2">
+        <v>548.21</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" t="s">
         <v>98</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>99</v>
-      </c>
-      <c r="F29" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -1948,11 +1965,11 @@
       <c r="B30">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="C30">
-        <v>182.98</v>
-      </c>
-      <c r="D30" t="s">
-        <v>11</v>
+      <c r="C30" s="2">
+        <v>395.8</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="E30" t="s">
         <v>12</v>
@@ -1968,11 +1985,11 @@
       <c r="B31">
         <v>0.2621</v>
       </c>
-      <c r="C31">
-        <v>575.86</v>
-      </c>
-      <c r="D31" t="s">
-        <v>54</v>
+      <c r="C31" s="2">
+        <v>356.1</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="E31" t="s">
         <v>55</v>
